--- a/samples/thornfield-continuation-fund-ii-call-7.xlsx
+++ b/samples/thornfield-continuation-fund-ii-call-7.xlsx
@@ -513,7 +513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -561,128 +561,139 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Reporting_Currency</v>
+        <v>GP_Name</v>
       </c>
       <c r="B5" t="str">
-        <v>USD</v>
+        <v>Thornfield GP II LLC</v>
       </c>
       <c r="C5" t="str">
-        <v>ISO code.</v>
+        <v>The general partner, named in the notice letter.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Call_Number</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
+        <v>Reporting_Currency</v>
+      </c>
+      <c r="B6" t="str">
+        <v>USD</v>
       </c>
       <c r="C6" t="str">
-        <v>Integer. Increment each call.</v>
+        <v>ISO code.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Call_Date</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-09-30</v>
+        <v>Call_Number</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
       </c>
       <c r="C7" t="str">
-        <v>Effective date of the call (YYYY-MM-DD).</v>
+        <v>Integer. Increment each call.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Payment_Due_Date</v>
+        <v>Call_Date</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-10-15</v>
+        <v>2026-09-30</v>
       </c>
       <c r="C8" t="str">
-        <v>When LP wires are due.</v>
+        <v>Effective date of the call (YYYY-MM-DD).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Default_Mgmt_Fee_Rate_Annual</v>
-      </c>
-      <c r="B9">
-        <v>0.015</v>
+        <v>Payment_Due_Date</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-10-15</v>
       </c>
       <c r="C9" t="str">
-        <v>Fraction. 0.015 = 1.50%.</v>
+        <v>When LP wires are due.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Default_Mgmt_Fee_Basis</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Commitment</v>
+        <v>Default_Mgmt_Fee_Rate_Annual</v>
+      </c>
+      <c r="B10">
+        <v>0.015</v>
       </c>
       <c r="C10" t="str">
-        <v>Commitment | Invested_Capital | NAV.</v>
+        <v>Fraction. 0.015 = 1.50%.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mgmt_Fee_Period_Fraction</v>
-      </c>
-      <c r="B11">
-        <v>0.25</v>
+        <v>Default_Mgmt_Fee_Basis</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Commitment</v>
       </c>
       <c r="C11" t="str">
-        <v>Portion of the annual fee called now. 0.25 = one quarter.</v>
+        <v>Commitment | Invested_Capital | NAV.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Org_Expense_Cap</v>
+        <v>Mgmt_Fee_Period_Fraction</v>
       </c>
       <c r="B12">
-        <v>200000</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="str">
-        <v>Lifetime cap on organizational expenses.</v>
+        <v>Portion of the annual fee called now. 0.25 = one quarter.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Rounding_Decimals</v>
+        <v>Org_Expense_Cap</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="C13" t="str">
-        <v>Decimal places for every allocation.</v>
+        <v>Lifetime cap on organizational expenses.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Rounding_Plug_LP_ID</v>
-      </c>
-      <c r="B14" t="str">
-        <v>LP04</v>
+        <v>Rounding_Decimals</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
-        <v>Absorbs the rounding residual. Largest commitment.</v>
+        <v>Decimal places for every allocation.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Rounding_Plug_LP_ID</v>
+      </c>
+      <c r="B15" t="str">
+        <v>LP04</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Absorbs the rounding residual. Largest commitment.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>Prepared_By</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B16" t="str">
         <v>Fund Administration</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C16" t="str">
         <v>Traceability.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/thornfield-continuation-fund-ii-call-7.xlsx
+++ b/samples/thornfield-continuation-fund-ii-call-7.xlsx
@@ -513,7 +513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -682,18 +682,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>Signatory_Name</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Alastair Finch</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Who signs the notice.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Signatory_Title</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Head of Fund Operations</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Their title, under the name.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Prepared_By</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B18" t="str">
         <v>Fund Administration</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C18" t="str">
         <v>Traceability.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/thornfield-continuation-fund-ii-call-7.xlsx
+++ b/samples/thornfield-continuation-fund-ii-call-7.xlsx
@@ -685,7 +685,7 @@
         <v>Signatory_Name</v>
       </c>
       <c r="B16" t="str">
-        <v>Alastair Finch</v>
+        <v>Baljeet Singh</v>
       </c>
       <c r="C16" t="str">
         <v>Who signs the notice.</v>
@@ -696,7 +696,7 @@
         <v>Signatory_Title</v>
       </c>
       <c r="B17" t="str">
-        <v>Head of Fund Operations</v>
+        <v>Fund Manager</v>
       </c>
       <c r="C17" t="str">
         <v>Their title, under the name.</v>
